--- a/themes/promo.xlsx
+++ b/themes/promo.xlsx
@@ -459,12 +459,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Со списком актуальных акций можно ознакомиться на [сайте Уралсиб](https://uralsib.ru/aktsii).</t>
+          <t xml:space="preserve">      Со списком актуальных акций можно ознакомиться на [сайте Уралсиб](https://uralsib.ru/aktsii)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>исправлена опечатка «актульных» → «актуальных»; добавлена точка в конце предложения</t>
+          <t>исправлена опечатка «актульных» → «актуальных»</t>
         </is>
       </c>
     </row>
